--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -851,10 +851,8 @@
           <t>Get Engineering Troop Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9802344177</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9802344177</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -869,10 +867,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9802344177</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9802344177</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -940,10 +936,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
@@ -954,7 +948,7 @@
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : REMOTE   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1003,7 +997,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1294,7 +1288,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Case : REMOTE   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="24" customWidth="1" min="32" max="32"/>
     <col width="27" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -974,6 +974,217 @@
       <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 9:36 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380806</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Aayush shrestha</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Aayush shrestha</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9843468465</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 09:36:28 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9843468465</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 09:07:13 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 09:36:28 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>27.67349</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Bhaktapur, ghatthaghar near by nepal telecom, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>aayushsth77@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>L51-6</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>85.37342</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 12h 29m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -988,7 +1199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -997,7 +1208,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1025,7 +1236,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1035,7 +1246,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1070,7 +1281,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>23h 44m</t>
+          <t>1d 6h 6m</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1318,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1122,203 +1333,311 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>IPTV Remote damage Issue</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>TKT1380952</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Get Engineering Troop Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>IPTV Remote damage Issue</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Case : REMOTE   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>29 Oct 2026 08:53:37 AM</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>28 Oct 2026 09:09:22 AM</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>29 Oct 2026 08:53:37 AM</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>23h 44m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TKT1380806</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Aayush shrestha</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 09:36:28 AM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 09:07:13 PM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 09:36:28 AM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>1d 12h 29m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -1044,10 +1044,8 @@
           <t>Aayush shrestha</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9843468465</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9843468465</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1062,10 +1060,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9843468465</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9843468465</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1082,10 +1078,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.67349</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.67349</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1141,48 +1135,247 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>L51-6</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.37342</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.37342</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 12h 29m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 9:54 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381026</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Sujal Pokherel</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Sujal Pokherel</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9861607603</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 09:54:03 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9861607603</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:02:51 AM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 09:54:03 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Near Panchpokhari Model Sec School P9GM+RQH, Gokarneshwor 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>n8e5s8n5@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>09:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L30-5</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>1d 12h 29m</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>23h 51m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1199,7 +1392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1236,7 +1429,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1439,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1281,7 +1474,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 6h 6m</t>
+          <t>1d 4h 1m</t>
         </is>
       </c>
     </row>
@@ -1322,10 +1515,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -1398,10 +1591,10 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -1607,14 +1800,14 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>29 Oct 2026 09:36:28 AM</t>
@@ -1638,6 +1831,73 @@
       <c r="M21" s="5" t="inlineStr">
         <is>
           <t>1d 12h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381026</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Sujal Pokherel</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 09:54:03 AM</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:02:51 AM</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 09:54:03 AM</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>23h 51m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1245,10 +1245,8 @@
           <t>Sujal Pokherel</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9861607603</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9861607603</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1263,10 +1261,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9861607603</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9861607603</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1338,10 +1334,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
@@ -1352,7 +1346,7 @@
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1401,7 +1395,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1867,7 +1861,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,18 +483,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW4"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="34" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -506,33 +506,33 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="24" customWidth="1" min="32" max="32"/>
-    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="28" customWidth="1" min="32" max="32"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -1372,6 +1372,1658 @@
       <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:47 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377993</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Yubraj Bhattarai</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Yubraj Bhattarai</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9851110377</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:47:38 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9851110377</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:14:38 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:47:38 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.73578</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>near Fishery Development Directorate  Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>ewarajbhattarai@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Mamata Bhujel</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>1,10</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.30316</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 33m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:42 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet not working  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>internet not working</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377795</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Rohit Oli</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Rohit Oli</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9857890358</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:42:32 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9857890358</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 09:57:04 AM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:42:32 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.75313</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Goldhunbga near Tarkeshwar Ward no. 5 office, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>rohitoli143@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Query For Secondary Router /Repeater</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>06:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L62-5</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.284</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet not working  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>4d 45m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet not working  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:38 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380909</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Bibek shrestha</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Bibek shrestha</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9819236730</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:38:20 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>LTP9819236730</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 08:08:50 AM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:38:20 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>near by N.S Parlour and Training Center - Beauty salon Lalitpur 44700, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>bibekcrestha05@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>10:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 29m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:01 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : router collection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>router collection</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381055</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Pedal budhathoki</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Pedal budhathoki</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9869643717</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:29:41 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>KLK9869643717</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:29:41 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:01:11 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Balaju bhatbhatine, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>Pes@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>ONT and Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>CDB553</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : router collection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>1d 31m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 31m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : router collection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:52 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>blank display</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379324</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Bhupendra oli</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Bhupendra oli</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9852027449</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:15:42 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9852027449</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:40:19 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:52:17 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Janajagriti Gyan Rashmi Secondary School - Government school P7JV+3QC kharibot station, Banasthhali</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>olibhupendra233@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>01:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>CDB287</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>2d 18h 36m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 11m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:51 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>blank display</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379324</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Bhupendra oli</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Bhupendra oli</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9852027449</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:15:42 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9852027449</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:40:19 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:52:17 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Janajagriti Gyan Rashmi Secondary School - Government school P7JV+3QC kharibot station, Banasthhali</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>olibhupendra233@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>01:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>CDB287</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>2d 18h 36m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 11m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:58 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380263</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Shrestha</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Shrestha</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9849304154</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:58:23 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9849304154</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:25:20 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:58:23 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.68994</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Near Motherland Hospital Pvt. Ltd, Thapagaon, Pepsicola Road, Pepsicola, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>surya204721@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>17:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Pramila Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L17-7</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.3633</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 33m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:31 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>SETUP BOX ISSUE</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380277</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Amrisha Karanjit</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Amrisha Karanjit</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9841285247</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:31:13 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9841285247</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:34:51 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:31:13 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.683009</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Madhyapur Thimi , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>amrishakaranjit@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>16:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L9-1</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.386192</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 56m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -1386,16 +3038,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1423,7 +3075,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -1433,7 +3085,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -1444,7 +3096,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -1456,7 +3108,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>14h 48m</t>
         </is>
       </c>
     </row>
@@ -1468,7 +3120,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 1m</t>
+          <t>2d 1m</t>
         </is>
       </c>
     </row>
@@ -1505,393 +3157,905 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Device Recovery</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="B12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>Device Recovery</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>ONT and Setup Box Recovery</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Query For Secondary Router /Repeater</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="D17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Detailed Solved / Handled Tickets List</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>TKT1380952</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Get Engineering Troop Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Remote damage Issue</t>
-        </is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Case : REMOTE   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>29 Oct 2026 08:53:37 AM</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 09:09:22 AM</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>29 Oct 2026 08:53:37 AM</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>23h 44m</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Detailed Solved / Handled Tickets List</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TKT1380952</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Get Engineering Troop Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : REMOTE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 08:53:37 AM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 09:09:22 AM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 08:53:37 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>23h 44m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>TKT1380806</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Aayush shrestha</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>29 Oct 2026 09:36:28 AM</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>27 Oct 2026 09:07:13 PM</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>29 Oct 2026 09:36:28 AM</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>1d 12h 29m</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>TKT1381026</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Sujal Pokherel</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>29 Oct 2026 09:54:03 AM</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>28 Oct 2026 10:02:51 AM</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>29 Oct 2026 09:54:03 AM</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>23h 51m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377795</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Rohit Oli</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Query For Secondary Router /Repeater</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet not working  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet not working  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:42:32 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 09:57:04 AM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:42:32 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>4d 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1380909</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Bibek shrestha</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:38:20 AM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 08:08:50 AM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:38:20 AM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379324</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Bhupendra oli</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:15:42 PM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:40:19 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:52:17 AM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>2d 18h 36m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1379324</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Bhupendra oli</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:15:42 PM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:40:19 PM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:52:17 AM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>2d 18h 36m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>2d 19h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380263</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Shrestha</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:58:23 AM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:25:20 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:58:23 AM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1380277</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Amrisha Karanjit</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:31:13 AM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:34:51 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:31:13 AM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>1d 20h 56m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW12"/>
+  <dimension ref="A1:AW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1442,10 +1442,8 @@
           <t>Yubraj Bhattarai</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9851110377</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9851110377</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1480,10 +1478,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.73578</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.73578</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1535,25 +1531,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>1,10</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.30316</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.30316000000001</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1649,10 +1641,8 @@
           <t>Rohit Oli</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9857890358</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9857890358</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1687,10 +1677,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.75313</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.75313</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1728,10 +1716,8 @@
           <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
-      <c r="AH6" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH6" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
@@ -1750,25 +1736,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>L62-5</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.284</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.28400000000001</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : internet not working  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -1864,10 +1846,8 @@
           <t>Bibek shrestha</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9819236730</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9819236730</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1957,10 +1937,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
@@ -1971,7 +1949,7 @@
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2057,20 +2035,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>Pedal budhathoki</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9869643717</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9869643717</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2156,10 +2128,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
@@ -2170,7 +2140,7 @@
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : router collection  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2266,10 +2236,8 @@
           <t>Bhupendra oli</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9852027449</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9852027449</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2359,10 +2327,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2373,7 +2339,7 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2469,10 +2435,8 @@
           <t>Bhupendra oli</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9852027449</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9852027449</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2562,10 +2526,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -2576,7 +2538,7 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2672,10 +2634,8 @@
           <t>Sanjeev Shrestha</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9849304154</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9849304154</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2710,10 +2670,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.68994</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.68994</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -2769,25 +2727,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L17-7</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.3633</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.3633</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -2883,10 +2837,8 @@
           <t>Amrisha Karanjit</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9841285247</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9841285247</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2921,10 +2873,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.683009</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.683009</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2980,50 +2930,355 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L9-1</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.386192</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.38619199999999</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 56m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>1d 20h 56m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:10 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr"/>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr"/>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr"/>
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AC13" s="3" t="inlineStr"/>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:30 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr"/>
+      <c r="V14" s="3" t="inlineStr"/>
+      <c r="W14" s="3" t="inlineStr"/>
+      <c r="X14" s="3" t="inlineStr"/>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr"/>
+      <c r="AA14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AC14" s="3" t="inlineStr"/>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr"/>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr"/>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr"/>
+      <c r="AN14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:07 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr"/>
+      <c r="V15" s="3" t="inlineStr"/>
+      <c r="W15" s="3" t="inlineStr"/>
+      <c r="X15" s="3" t="inlineStr"/>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr"/>
+      <c r="AA15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AC15" s="3" t="inlineStr"/>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
+      <c r="AM15" s="3" t="inlineStr"/>
+      <c r="AN15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3047,7 +3302,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3075,7 +3330,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -3096,7 +3351,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -3208,84 +3463,75 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Device Recovery</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>ONT and Setup Box Recovery</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Device Recovery</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>ONT and Setup Box Recovery</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3297,41 +3543,41 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3589,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -3366,249 +3612,153 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1380952</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Get Engineering Troop Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Remote damage Issue</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : REMOTE   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>29 Oct 2026 08:53:37 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 09:09:22 AM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>29 Oct 2026 08:53:37 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>23h 44m</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1380806</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Aayush shrestha</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>29 Oct 2026 09:36:28 AM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>27 Oct 2026 09:07:13 PM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>29 Oct 2026 09:36:28 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>1d 12h 29m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1381026</t>
+          <t>TKT1380952</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Sujal Pokherel</t>
+          <t>Get Engineering Troop Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -3628,22 +3778,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : REMOTE   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 09:54:03 AM</t>
+          <t>29 Oct 2026 08:53:37 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:02:51 AM</t>
+          <t>28 Oct 2026 09:09:22 AM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 09:54:03 AM</t>
+          <t>29 Oct 2026 08:53:37 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -3653,19 +3803,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>23h 51m</t>
+          <t>23h 44m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1377795</t>
+          <t>TKT1380806</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Rohit Oli</t>
+          <t>Aayush shrestha</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3675,7 +3825,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -3690,27 +3840,27 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Case : internet not working  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : internet not working  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:42:32 AM</t>
+          <t>29 Oct 2026 09:36:28 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>25 Oct 2026 09:57:04 AM</t>
+          <t>27 Oct 2026 09:07:13 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:42:32 AM</t>
+          <t>29 Oct 2026 09:36:28 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -3720,19 +3870,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>4d 45m</t>
+          <t>1d 12h 29m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1380909</t>
+          <t>TKT1381026</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Bibek shrestha</t>
+          <t>Sujal Pokherel</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -3757,27 +3907,27 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:38:20 AM</t>
+          <t>29 Oct 2026 09:54:03 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 08:08:50 AM</t>
+          <t>28 Oct 2026 10:02:51 AM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:38:20 AM</t>
+          <t>29 Oct 2026 09:54:03 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -3787,153 +3937,153 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>1d 2h 29m</t>
+          <t>23h 51m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1379324</t>
+          <t>TKT1377795</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Bhupendra oli</t>
+          <t>Rohit Oli</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+          <t>Case : internet not working  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 04:15:42 PM</t>
+          <t>29 Oct 2026 10:42:32 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 03:40:19 PM</t>
+          <t>25 Oct 2026 09:57:04 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:52:17 AM</t>
+          <t>29 Oct 2026 10:42:32 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2d 18h 36m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2d 19h 11m</t>
+          <t>4d 45m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1379324</t>
+          <t>TKT1380909</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Bhupendra oli</t>
+          <t>Bibek shrestha</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 04:15:42 PM</t>
+          <t>29 Oct 2026 10:38:20 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 03:40:19 PM</t>
+          <t>28 Oct 2026 08:08:50 AM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:52:17 AM</t>
+          <t>29 Oct 2026 10:38:20 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2d 18h 36m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>2d 19h 11m</t>
+          <t>1d 2h 29m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1380263</t>
+          <t>TKT1379324</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Shrestha</t>
+          <t>Bhupendra oli</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3943,117 +4093,251 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Shashikant Chaudhary</t>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:58:23 AM</t>
+          <t>26 Oct 2026 04:15:42 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>27 Oct 2026 01:25:20 PM</t>
+          <t>26 Oct 2026 03:40:19 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:58:23 AM</t>
+          <t>29 Oct 2026 10:52:17 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 18h 36m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 33m</t>
+          <t>2d 19h 11m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>TKT1379324</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Bhupendra oli</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:15:42 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:40:19 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:52:17 AM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>2d 18h 36m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>2d 19h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380263</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Shrestha</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:58:23 AM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:25:20 PM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:58:23 AM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t>TKT1380277</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Amrisha Karanjit</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>29 Oct 2026 10:31:13 AM</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>27 Oct 2026 01:34:51 PM</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>29 Oct 2026 10:31:13 AM</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="M35" s="5" t="inlineStr">
         <is>
           <t>1d 20h 56m</t>
         </is>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW15"/>
+  <dimension ref="A1:AW16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3282,6 +3282,109 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:30 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr"/>
+      <c r="V16" s="3" t="inlineStr"/>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr"/>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr"/>
+      <c r="AA16" s="3" t="inlineStr"/>
+      <c r="AB16" s="3" t="inlineStr"/>
+      <c r="AC16" s="3" t="inlineStr"/>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr"/>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr"/>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
+      <c r="AM16" s="3" t="inlineStr"/>
+      <c r="AN16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr"/>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3330,7 +3433,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -3351,7 +3454,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW16"/>
+  <dimension ref="A1:AW20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="27" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3385,6 +3385,846 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:34 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380100</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Pradip Poudel</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Pradip Poudel</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9849120697</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:33:59 AM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9849120697</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:29:16 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:33:59 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.6655</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Near Budhi Bikash Football Ground, Lagankhel, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>grng_pradip@yahoo.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>20:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>CDB927</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.32093</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>2d 4m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:44 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379150</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Hotel Parbat Samjhana</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Hotel Parbat Samjhana</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9851322044</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:44:58 AM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9808547970</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:14:24 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:44:58 AM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.73037</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Gongabu, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>shresthabipin227@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>04:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>L33-2</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.31158</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 30m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:36 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>wifi6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379142</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Hotel Parbat Samjhana</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Hotel Parbat Samjhana</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9851322044</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:36:37 AM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>hotelparbatsamjhana_fttx</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:08:44 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:36:37 AM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.73029</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Telecom Mitranagar Marg, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>shresthabipin227@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>04:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>L33-2</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.31154</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 27m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:43 AM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381095</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Rajiv Pandey</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Rajiv Pandey</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9745326628</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:53:30 AM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9745326658</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:53:30 AM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:43:27 AM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.67518</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Near Bijeshwori Gyan Mandir Sainik Mahavidyalaya, Sainik Awas Marg, Kathmandu, Bagmati, Central, Nep</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>10:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>3,14</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.378529</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3396,7 +4236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3405,7 +4245,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3433,7 +4273,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -3443,7 +4283,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -3454,7 +4294,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -3466,7 +4306,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>14h 48m</t>
+          <t>12h 9m</t>
         </is>
       </c>
     </row>
@@ -3478,7 +4318,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 1m</t>
+          <t>2d 1h 42m</t>
         </is>
       </c>
     </row>
@@ -3537,14 +4377,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -3673,14 +4513,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -4446,6 +5286,274 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380100</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Pradip Poudel</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:33:59 AM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:29:16 AM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:33:59 AM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>2d 4m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1379150</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Hotel Parbat Samjhana</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:44:58 AM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:14:24 PM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:44:58 AM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>2d 22h 30m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379142</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Hotel Parbat Samjhana</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:36:37 AM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:08:44 PM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:36:37 AM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1381095</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Rajiv Pandey</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:53:30 AM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:53:30 AM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:43:27 AM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW20"/>
+  <dimension ref="A1:AW21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3452,10 +3452,8 @@
           <t>Pradip Poudel</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9849120697</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9849120697</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3490,10 +3488,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.6655</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.6655</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -3549,25 +3545,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>CDB927</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.32093</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.32093</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -3663,10 +3655,8 @@
           <t>Hotel Parbat Samjhana</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9851322044</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9851322044</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -3701,10 +3691,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.73037</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.73037</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -3760,25 +3748,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>L33-2</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.31158</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.31158000000001</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -3874,10 +3858,8 @@
           <t>Hotel Parbat Samjhana</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9851322044</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9851322044</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -3912,10 +3894,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.73029</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.73029</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -3971,25 +3951,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>L33-2</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.31154</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.31153999999999</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4085,10 +4061,8 @@
           <t>Rajiv Pandey</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9745326628</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9745326628</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4123,10 +4097,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.67518</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.67518</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -4178,48 +4150,247 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>3,14</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.378529</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.378529</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS20" s="3" t="inlineStr">
-        <is>
-          <t>1d 49m</t>
-        </is>
-      </c>
-      <c r="AT20" s="3" t="inlineStr">
-        <is>
-          <t>1d 49m</t>
-        </is>
-      </c>
-      <c r="AU20" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV20" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:49 AM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380168</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Ravi  Bajracharya</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Ravi  Bajracharya</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9841750330</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:49:48 AM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>LTP9841750330</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 12:28:42 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:49:48 AM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Lagan khel (Kumari pati vanda ali mathi), Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>ravibajracharya7@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>19:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>CDB923</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -4236,7 +4407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4273,7 +4444,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -4283,7 +4454,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -4294,7 +4465,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4477,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>12h 9m</t>
+          <t>11h 17m</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4489,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 42m</t>
+          <t>2d 1h 31m</t>
         </is>
       </c>
     </row>
@@ -4377,14 +4548,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -4513,14 +4684,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5490,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -5386,7 +5557,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -5453,7 +5624,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -5520,14 +5691,14 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>28 Oct 2026 10:53:30 AM</t>
@@ -5551,6 +5722,73 @@
       <c r="M39" s="5" t="inlineStr">
         <is>
           <t>1d 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380168</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Ravi  Bajracharya</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:49:48 AM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 12:28:42 PM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:49:48 AM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW21"/>
+  <dimension ref="A1:AW25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -513,11 +513,11 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="28" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="29" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -532,7 +532,7 @@
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -4260,10 +4260,8 @@
           <t>Ravi  Bajracharya</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9841750330</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9841750330</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4353,10 +4351,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -4367,30 +4363,870 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS21" s="3" t="inlineStr">
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:03 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB return  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>STB return</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380048</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Kriti Shakya</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Kriti Shakya</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9841538314</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:03:39 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9841538314</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:01:01 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:03:39 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.661455</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Army Physical Training and Sports Centre, Lalitpur 4470044700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>21:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>CDB946</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.323686</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB return  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT21" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 21m</t>
-        </is>
-      </c>
-      <c r="AU21" s="3" t="inlineStr">
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 2m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW21" s="3" t="inlineStr">
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB return  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:06 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky to NETTV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>sky to NETTV</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379566</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Preeti Bajracharya</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Preeti Bajracharya</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9841384000</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:11:34 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9841384000</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 06:19:57 PM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:11:34 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.69575</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>customer experience sales</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Teku Pachali Galli, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>preetibajracharya@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Yaman Bhandari</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>CDB044</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.30426</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky to NETTV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>2d 17h 51m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky to NETTV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:05 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>remote issue</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379980</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Amatya</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Amatya</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9860558291</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:05:15 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9860558291</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 10:25:07 AM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:05:15 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Basantapur Near Shree Kumari Secondary School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>sujanamatya46@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>21:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>CDB025</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 40m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:04 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378950</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Victim Support &amp; Rehalibitation Program</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Victim Support &amp; Rehalibitation Program</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9841345531</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:04:18 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9841345531</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 10:47:59 AM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:04:18 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.723737</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Tekkon Technologies,Shree Marga, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>prakashtamang@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>07:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>2,16</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.324953</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 16m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -4407,11 +5243,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -4444,7 +5280,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -4454,7 +5290,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -4465,7 +5301,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.8%</t>
         </is>
       </c>
     </row>
@@ -4477,7 +5313,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>11h 17m</t>
+          <t>9h 17m</t>
         </is>
       </c>
     </row>
@@ -4489,7 +5325,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 31m</t>
+          <t>2d 2h 54m</t>
         </is>
       </c>
     </row>
@@ -4548,14 +5384,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>91.7%</t>
         </is>
       </c>
     </row>
@@ -4566,10 +5402,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -4578,97 +5414,92 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
       <c r="B13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Device Recovery</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>ONT and Setup Box Recovery</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Device Recovery</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>ONT and Setup Box Recovery</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4680,41 +5511,41 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -4726,14 +5557,14 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -4749,14 +5580,14 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -4765,248 +5596,160 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
       <c r="C23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1380952</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Get Engineering Troop Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Remote damage Issue</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : REMOTE   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>29 Oct 2026 08:53:37 AM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 09:09:22 AM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>29 Oct 2026 08:53:37 AM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>23h 44m</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>TKT1380806</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Aayush shrestha</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>29 Oct 2026 09:36:28 AM</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>27 Oct 2026 09:07:13 PM</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>29 Oct 2026 09:36:28 AM</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>1d 12h 29m</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1381026</t>
+          <t>TKT1380952</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Sujal Pokherel</t>
+          <t>Get Engineering Troop Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -5026,22 +5769,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : REMOTE   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 09:54:03 AM</t>
+          <t>29 Oct 2026 08:53:37 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:02:51 AM</t>
+          <t>28 Oct 2026 09:09:22 AM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 09:54:03 AM</t>
+          <t>29 Oct 2026 08:53:37 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -5051,19 +5794,19 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>23h 51m</t>
+          <t>23h 44m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1377795</t>
+          <t>TKT1380806</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Rohit Oli</t>
+          <t>Aayush shrestha</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5073,7 +5816,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -5093,22 +5836,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : internet not working  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:42:32 AM</t>
+          <t>29 Oct 2026 09:36:28 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>25 Oct 2026 09:57:04 AM</t>
+          <t>27 Oct 2026 09:07:13 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:42:32 AM</t>
+          <t>29 Oct 2026 09:36:28 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -5118,19 +5861,19 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>4d 45m</t>
+          <t>1d 12h 29m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1380909</t>
+          <t>TKT1381026</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Bibek shrestha</t>
+          <t>Sujal Pokherel</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -5160,22 +5903,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:38:20 AM</t>
+          <t>29 Oct 2026 09:54:03 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 08:08:50 AM</t>
+          <t>28 Oct 2026 10:02:51 AM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:38:20 AM</t>
+          <t>29 Oct 2026 09:54:03 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -5185,39 +5928,39 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>1d 2h 29m</t>
+          <t>23h 51m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1379324</t>
+          <t>TKT1377795</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Bhupendra oli</t>
+          <t>Rohit Oli</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -5227,64 +5970,64 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+          <t>Case : internet not working  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 04:15:42 PM</t>
+          <t>29 Oct 2026 10:42:32 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 03:40:19 PM</t>
+          <t>25 Oct 2026 09:57:04 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:52:17 AM</t>
+          <t>29 Oct 2026 10:42:32 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2d 18h 36m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2d 19h 11m</t>
+          <t>4d 45m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1379324</t>
+          <t>TKT1380909</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Bhupendra oli</t>
+          <t>Bibek shrestha</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -5294,44 +6037,44 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 04:15:42 PM</t>
+          <t>29 Oct 2026 10:38:20 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 03:40:19 PM</t>
+          <t>28 Oct 2026 08:08:50 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:52:17 AM</t>
+          <t>29 Oct 2026 10:38:20 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>2d 18h 36m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>2d 19h 11m</t>
+          <t>1d 2h 29m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1380263</t>
+          <t>TKT1379324</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Shrestha</t>
+          <t>Bhupendra oli</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5341,17 +6084,17 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -5361,44 +6104,44 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Shashikant Chaudhary</t>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:58:23 AM</t>
+          <t>26 Oct 2026 04:15:42 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>27 Oct 2026 01:25:20 PM</t>
+          <t>26 Oct 2026 03:40:19 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:58:23 AM</t>
+          <t>29 Oct 2026 10:52:17 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 18h 36m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 33m</t>
+          <t>2d 19h 11m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1380277</t>
+          <t>TKT1379324</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Amrisha Karanjit</t>
+          <t>Bhupendra oli</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -5413,12 +6156,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -5428,54 +6171,54 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:31:13 AM</t>
+          <t>26 Oct 2026 04:15:42 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>27 Oct 2026 01:34:51 PM</t>
+          <t>26 Oct 2026 03:40:19 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:31:13 AM</t>
+          <t>29 Oct 2026 10:52:17 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 18h 36m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1d 20h 56m</t>
+          <t>2d 19h 11m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1380100</t>
+          <t>TKT1380263</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Pradip Poudel</t>
+          <t>Sanjeev Shrestha</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -5495,22 +6238,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : no light blinking  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 11:33:59 AM</t>
+          <t>29 Oct 2026 10:58:23 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>27 Oct 2026 11:29:16 AM</t>
+          <t>27 Oct 2026 01:25:20 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 11:33:59 AM</t>
+          <t>29 Oct 2026 10:58:23 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -5520,29 +6263,29 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2d 4m</t>
+          <t>1d 21h 33m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1379150</t>
+          <t>TKT1380277</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Hotel Parbat Samjhana</t>
+          <t>Amrisha Karanjit</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -5562,22 +6305,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 11:44:58 AM</t>
+          <t>29 Oct 2026 10:31:13 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 01:14:24 PM</t>
+          <t>27 Oct 2026 01:34:51 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 11:44:58 AM</t>
+          <t>29 Oct 2026 10:31:13 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -5587,19 +6330,19 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>2d 22h 30m</t>
+          <t>1d 20h 56m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1379142</t>
+          <t>TKT1380100</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Hotel Parbat Samjhana</t>
+          <t>Pradip Poudel</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -5629,22 +6372,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 11:36:37 AM</t>
+          <t>29 Oct 2026 11:33:59 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 01:08:44 PM</t>
+          <t>27 Oct 2026 11:29:16 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 11:36:37 AM</t>
+          <t>29 Oct 2026 11:33:59 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5654,19 +6397,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2d 22h 27m</t>
+          <t>2d 4m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1381095</t>
+          <t>TKT1379150</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Rajiv Pandey</t>
+          <t>Hotel Parbat Samjhana</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -5681,12 +6424,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -5696,99 +6439,434 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:53:30 AM</t>
+          <t>29 Oct 2026 11:44:58 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:53:30 AM</t>
+          <t>26 Oct 2026 01:14:24 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 11:43:27 AM</t>
+          <t>29 Oct 2026 11:44:58 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>1d 49m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>1d 49m</t>
+          <t>2d 22h 30m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t>TKT1379142</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Hotel Parbat Samjhana</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:36:37 AM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:08:44 PM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:36:37 AM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1381095</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Rajiv Pandey</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:53:30 AM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:53:30 AM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:43:27 AM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
           <t>TKT1380168</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Ravi  Bajracharya</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>29 Oct 2026 11:49:48 AM</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>27 Oct 2026 12:28:42 PM</t>
         </is>
       </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="K42" s="3" t="inlineStr">
         <is>
           <t>29 Oct 2026 11:49:48 AM</t>
         </is>
       </c>
-      <c r="L40" s="3" t="inlineStr">
+      <c r="L42" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
+      <c r="M42" s="3" t="inlineStr">
         <is>
           <t>1d 23h 21m</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TKT1380048</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Kriti Shakya</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Case : STB return  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : STB return  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:03:39 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:01:01 AM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:03:39 PM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>2d 1h 2m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379980</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Amatya</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:05:15 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 10:25:07 AM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:05:15 PM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 40m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TKT1378950</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Victim Support &amp; Rehalibitation Program</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:04:18 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 10:47:59 AM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:04:18 PM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>3d 1h 16m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW25"/>
+  <dimension ref="A1:AW28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="20" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -4459,10 +4459,8 @@
           <t>Kriti Shakya</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9841538314</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9841538314</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4497,10 +4495,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.661455</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.661455</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -4552,25 +4548,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>CDB946</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.323686</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.323686</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : STB return  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -4666,10 +4658,8 @@
           <t>Preeti Bajracharya</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9841384000</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9841384000</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -4704,10 +4694,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.69575</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.69575</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -4745,10 +4733,8 @@
           <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
-      <c r="AH23" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH23" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI23" s="3" t="inlineStr"/>
       <c r="AJ23" s="3" t="inlineStr"/>
@@ -4763,25 +4749,21 @@
           <t>Yaman Bhandari</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>CDB044</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.30426</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.30426</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : sky to NETTV  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -4877,10 +4859,8 @@
           <t>Sujan Amatya</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9860558291</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9860558291</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -4915,10 +4895,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -4974,25 +4952,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>CDB025</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : remote issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5088,10 +5062,8 @@
           <t>Victim Support &amp; Rehalibitation Program</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9841345531</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9841345531</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5126,10 +5098,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.723737</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.723737</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -5185,50 +5155,651 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>2,16</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.324953</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.32495299999999</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 16m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS25" s="3" t="inlineStr">
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:30 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV issue</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380003</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Prabat Bhandari</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Prabat Bhandari</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9851089669</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:30:13 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9851089669</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 10:32:40 AM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:30:13 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>27.676569404736984,85.36483187861175, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>21:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L21-8</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr"/>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT25" s="3" t="inlineStr">
-        <is>
-          <t>3d 1h 16m</t>
-        </is>
-      </c>
-      <c r="AU25" s="3" t="inlineStr">
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 57m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV25" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW25" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:27 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>iptv setbox issue</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380270</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Habib Laheri</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Habib Laheri</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9851029384</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:32:11 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>IC9851029384A</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:28:56 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:27:49 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.70816</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Asan near to balkumari madir, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr"/>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr"/>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.31304</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 55m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 58m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:26 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381481</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Sita Subedi</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Sita Subedi</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9841184071</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:26:07 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841184071</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 04:15:05 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:26:07 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Yangalchowk,  Bhotebahal, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>9841184071@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>06:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Pramila Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>CDB022</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>20h 11m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5280,7 +5851,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -5290,7 +5861,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -5301,7 +5872,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.4%</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5884,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 17m</t>
+          <t>8h 19m</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5896,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 54m</t>
+          <t>2d 1h 14m</t>
         </is>
       </c>
     </row>
@@ -5402,14 +5973,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -5420,14 +5991,14 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5607,14 +6178,14 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -5642,181 +6213,137 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
       <c r="C25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>TKT1380952</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Get Engineering Troop Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Remote damage Issue</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : REMOTE   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>29 Oct 2026 08:53:37 AM</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 09:09:22 AM</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>29 Oct 2026 08:53:37 AM</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>23h 44m</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1380806</t>
+          <t>TKT1380952</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Aayush shrestha</t>
+          <t>Get Engineering Troop Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -5836,22 +6363,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : REMOTE   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 09:36:28 AM</t>
+          <t>29 Oct 2026 08:53:37 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>27 Oct 2026 09:07:13 PM</t>
+          <t>28 Oct 2026 09:09:22 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 09:36:28 AM</t>
+          <t>29 Oct 2026 08:53:37 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -5861,19 +6388,19 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1d 12h 29m</t>
+          <t>23h 44m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1381026</t>
+          <t>TKT1380806</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Sujal Pokherel</t>
+          <t>Aayush shrestha</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -5903,22 +6430,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 09:54:03 AM</t>
+          <t>29 Oct 2026 09:36:28 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:02:51 AM</t>
+          <t>27 Oct 2026 09:07:13 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 09:54:03 AM</t>
+          <t>29 Oct 2026 09:36:28 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -5928,19 +6455,19 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>23h 51m</t>
+          <t>1d 12h 29m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1377795</t>
+          <t>TKT1381026</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Rohit Oli</t>
+          <t>Sujal Pokherel</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5950,7 +6477,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -5970,22 +6497,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : internet not working  has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:42:32 AM</t>
+          <t>29 Oct 2026 09:54:03 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>25 Oct 2026 09:57:04 AM</t>
+          <t>28 Oct 2026 10:02:51 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:42:32 AM</t>
+          <t>29 Oct 2026 09:54:03 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -5995,19 +6522,19 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>4d 45m</t>
+          <t>23h 51m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1380909</t>
+          <t>TKT1377795</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Bibek shrestha</t>
+          <t>Rohit Oli</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -6017,7 +6544,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -6037,22 +6564,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : internet not working  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:38:20 AM</t>
+          <t>29 Oct 2026 10:42:32 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 08:08:50 AM</t>
+          <t>25 Oct 2026 09:57:04 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:38:20 AM</t>
+          <t>29 Oct 2026 10:42:32 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -6062,39 +6589,39 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>1d 2h 29m</t>
+          <t>4d 45m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1379324</t>
+          <t>TKT1380909</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Bhupendra oli</t>
+          <t>Bibek shrestha</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -6104,32 +6631,32 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 04:15:42 PM</t>
+          <t>29 Oct 2026 10:38:20 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 03:40:19 PM</t>
+          <t>28 Oct 2026 08:08:50 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:52:17 AM</t>
+          <t>29 Oct 2026 10:38:20 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2d 18h 36m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2d 19h 11m</t>
+          <t>1d 2h 29m</t>
         </is>
       </c>
     </row>
@@ -6203,12 +6730,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1380263</t>
+          <t>TKT1379324</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Shrestha</t>
+          <t>Bhupendra oli</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -6218,17 +6745,17 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -6238,44 +6765,44 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Shashikant Chaudhary</t>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:58:23 AM</t>
+          <t>26 Oct 2026 04:15:42 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>27 Oct 2026 01:25:20 PM</t>
+          <t>26 Oct 2026 03:40:19 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:58:23 AM</t>
+          <t>29 Oct 2026 10:52:17 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 18h 36m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 33m</t>
+          <t>2d 19h 11m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1380277</t>
+          <t>TKT1380263</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Amrisha Karanjit</t>
+          <t>Sanjeev Shrestha</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -6285,7 +6812,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -6305,22 +6832,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
+          <t>Case : no light blinking  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:31:13 AM</t>
+          <t>29 Oct 2026 10:58:23 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>27 Oct 2026 01:34:51 PM</t>
+          <t>27 Oct 2026 01:25:20 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 10:31:13 AM</t>
+          <t>29 Oct 2026 10:58:23 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -6330,29 +6857,29 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>1d 20h 56m</t>
+          <t>1d 21h 33m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1380100</t>
+          <t>TKT1380277</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Pradip Poudel</t>
+          <t>Amrisha Karanjit</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -6372,22 +6899,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : SETUP BOX ISSUE   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 11:33:59 AM</t>
+          <t>29 Oct 2026 10:31:13 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>27 Oct 2026 11:29:16 AM</t>
+          <t>27 Oct 2026 01:34:51 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 11:33:59 AM</t>
+          <t>29 Oct 2026 10:31:13 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -6397,19 +6924,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2d 4m</t>
+          <t>1d 20h 56m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1379150</t>
+          <t>TKT1380100</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Hotel Parbat Samjhana</t>
+          <t>Pradip Poudel</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -6439,22 +6966,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 11:44:58 AM</t>
+          <t>29 Oct 2026 11:33:59 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 01:14:24 PM</t>
+          <t>27 Oct 2026 11:29:16 AM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 11:44:58 AM</t>
+          <t>29 Oct 2026 11:33:59 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -6464,14 +6991,14 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>2d 22h 30m</t>
+          <t>2d 4m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1379142</t>
+          <t>TKT1379150</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -6506,22 +7033,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 11:36:37 AM</t>
+          <t>29 Oct 2026 11:44:58 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 01:08:44 PM</t>
+          <t>26 Oct 2026 01:14:24 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 11:36:37 AM</t>
+          <t>29 Oct 2026 11:44:58 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -6531,19 +7058,19 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2d 22h 27m</t>
+          <t>2d 22h 30m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1381095</t>
+          <t>TKT1379142</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Rajiv Pandey</t>
+          <t>Hotel Parbat Samjhana</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -6558,12 +7085,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -6573,44 +7100,44 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:53:30 AM</t>
+          <t>29 Oct 2026 11:36:37 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:53:30 AM</t>
+          <t>26 Oct 2026 01:08:44 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 11:43:27 AM</t>
+          <t>29 Oct 2026 11:36:37 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>1d 49m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>1d 49m</t>
+          <t>2d 22h 27m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1380168</t>
+          <t>TKT1381095</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Ravi  Bajracharya</t>
+          <t>Rajiv Pandey</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -6625,12 +7152,12 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -6640,44 +7167,44 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 11:49:48 AM</t>
+          <t>28 Oct 2026 10:53:30 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>27 Oct 2026 12:28:42 PM</t>
+          <t>28 Oct 2026 10:53:30 AM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 11:49:48 AM</t>
+          <t>29 Oct 2026 11:43:27 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 49m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 21m</t>
+          <t>1d 49m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1380048</t>
+          <t>TKT1380168</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Kriti Shakya</t>
+          <t>Ravi  Bajracharya</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -6702,27 +7229,27 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Case : STB return  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : STB return  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 12:03:39 PM</t>
+          <t>29 Oct 2026 11:49:48 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>27 Oct 2026 11:01:01 AM</t>
+          <t>27 Oct 2026 12:28:42 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 12:03:39 PM</t>
+          <t>29 Oct 2026 11:49:48 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -6732,29 +7259,29 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>2d 1h 2m</t>
+          <t>1d 23h 21m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1379980</t>
+          <t>TKT1380048</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Sujan Amatya</t>
+          <t>Kriti Shakya</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -6769,27 +7296,27 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Case : remote issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : remote issue  has been updated by Chandramani Tharu</t>
+          <t>Case : STB return  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 12:05:15 PM</t>
+          <t>29 Oct 2026 12:03:39 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>27 Oct 2026 10:25:07 AM</t>
+          <t>27 Oct 2026 11:01:01 AM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 12:05:15 PM</t>
+          <t>29 Oct 2026 12:03:39 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -6799,74 +7326,275 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 40m</t>
+          <t>2d 1h 2m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
+          <t>TKT1379980</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Sujan Amatya</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : remote issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:05:15 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 10:25:07 AM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:05:15 PM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>2d 1h 40m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
           <t>TKT1378950</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Victim Support &amp; Rehalibitation Program</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>29 Oct 2026 12:04:18 PM</t>
         </is>
       </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>26 Oct 2026 10:47:59 AM</t>
         </is>
       </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="K46" s="3" t="inlineStr">
         <is>
           <t>29 Oct 2026 12:04:18 PM</t>
         </is>
       </c>
-      <c r="L45" s="5" t="inlineStr">
+      <c r="L46" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M45" s="5" t="inlineStr">
+      <c r="M46" s="3" t="inlineStr">
         <is>
           <t>3d 1h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TKT1380003</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Prabat Bhandari</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:30:13 PM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 10:32:40 AM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:30:13 PM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>2d 1h 57m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381481</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Sita Subedi</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:26:07 PM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 04:15:05 PM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:26:07 PM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>20h 11m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW28"/>
+  <dimension ref="A1:AW31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5265,10 +5265,8 @@
           <t>Prabat Bhandari</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9851089669</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9851089669</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5354,10 +5352,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
@@ -5368,7 +5364,7 @@
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -5464,10 +5460,8 @@
           <t>Habib Laheri</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9851029384</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9851029384</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5502,10 +5496,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.70816</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.70816</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -5553,25 +5545,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>3,13</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.31304</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.31304</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv setbox issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -5667,10 +5655,8 @@
           <t>Sita Subedi</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9841184071</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9841184071</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -5760,10 +5746,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
@@ -5774,32 +5758,637 @@
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>20h 11m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS28" s="3" t="inlineStr">
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:41 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380887</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Ushan Dev Shakya</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Ushan Dev Shakya</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9803034566</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:41:06 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9803034566</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 07:48:25 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:41:06 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.66594</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Machaga, Lunkhusi Near BNB hospital, near star food land, , Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>usnshakya4@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>12:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>CDB962</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.33006</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT28" s="3" t="inlineStr">
-        <is>
-          <t>20h 11m</t>
-        </is>
-      </c>
-      <c r="AU28" s="3" t="inlineStr">
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV28" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW28" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:36 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : red light issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>red light issue</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380592</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Rajkumar Deshar</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Rajkumar Deshar</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9841400677</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 05:24:46 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9841400677</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 05:20:39 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:36:33 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Kumari mandir, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : red light issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 11m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 15m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : red light issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:35 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378084</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Raunak Maskay</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Raunak Maskay</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9841126820</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:10:58 AM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841126820</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:05:16 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:35:00 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr"/>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Bajaj Lainchaur (Star Auto Enterprises) Nagpokhari Marg, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>raunakmaskay@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>CDB011</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>1h 24m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 29m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -5814,7 +6403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5851,7 +6440,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -5861,7 +6450,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -5872,7 +6461,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +6473,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h 19m</t>
+          <t>7h 54m</t>
         </is>
       </c>
     </row>
@@ -5896,7 +6485,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 14m</t>
+          <t>2d 13m</t>
         </is>
       </c>
     </row>
@@ -5955,14 +6544,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -5973,14 +6562,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -6109,14 +6698,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -6178,14 +6767,14 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>4</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -7497,7 +8086,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -7564,14 +8153,14 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
           <t>29 Oct 2026 12:26:07 PM</t>
@@ -7595,6 +8184,73 @@
       <c r="M48" s="3" t="inlineStr">
         <is>
           <t>20h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TKT1380887</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Ushan Dev Shakya</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:41:06 PM</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 07:48:25 AM</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:41:06 PM</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW31"/>
+  <dimension ref="A1:AW33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="31" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -5854,10 +5854,8 @@
           <t>Ushan Dev Shakya</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9803034566</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9803034566</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -5892,10 +5890,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>27.66594</t>
-        </is>
+      <c r="Y29" s="3" t="n">
+        <v>27.66594</v>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
@@ -5951,25 +5947,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>CDB962</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.33006</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.33006</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -6065,10 +6057,8 @@
           <t>Rajkumar Deshar</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9841400677</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9841400677</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6150,10 +6140,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -6164,7 +6152,7 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : red light issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -6260,10 +6248,8 @@
           <t>Raunak Maskay</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9841126820</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9841126820</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6349,10 +6335,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
@@ -6363,30 +6347,452 @@
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>1h 24m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 29m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS31" s="3" t="inlineStr">
-        <is>
-          <t>1h 24m</t>
-        </is>
-      </c>
-      <c r="AT31" s="3" t="inlineStr">
-        <is>
-          <t>3d 22h 29m</t>
-        </is>
-      </c>
-      <c r="AU31" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV31" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:59 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgarde   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgarde</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379172</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Bikash Thapaliya</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Bikash Thapaliya</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9841873614</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:59:37 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9841873614</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:30:41 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:59:37 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.73875</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>jiban khatiwada homestay - Wholesaler Q852+G4G Tarakeshwar, Bagmati Province 44600, Kathmandu, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>bikashthapaliya123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>05:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>L10-1</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.30291</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgarde   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 28m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgarde   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:59 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : TV issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>TV issue</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381638</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9861926855</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:39:01 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>DRZ9861926855</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:39:01 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:59:25 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.70284</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Kalimati 27.7027679, 85.2861990 - Near Jehovah's Witnesses Society,Kalimati,Kathmandu - Kathmandu Me</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>5sos.cyrus@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>05:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Yaman Bhandari</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.2862</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : TV issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>19h 20m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>19h 20m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : TV issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -6403,7 +6809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6440,7 +6846,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -6450,7 +6856,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -6461,7 +6867,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -6473,7 +6879,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 54m</t>
+          <t>8h 3m</t>
         </is>
       </c>
     </row>
@@ -6485,7 +6891,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 13m</t>
+          <t>1d 23h 58m</t>
         </is>
       </c>
     </row>
@@ -6544,14 +6950,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
@@ -6562,14 +6968,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -6698,14 +7104,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -6767,14 +7173,14 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -8220,14 +8626,14 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
           <t>29 Oct 2026 12:41:06 PM</t>
@@ -8251,6 +8657,140 @@
       <c r="M49" s="5" t="inlineStr">
         <is>
           <t>1d 4h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379172</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Bikash Thapaliya</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgarde   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgarde   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:59:37 PM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:30:41 PM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:59:37 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TKT1381638</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Case : TV issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Case : TV issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:39:01 PM</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:39:01 PM</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 12:59:25 PM</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>19h 20m</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>19h 20m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW33"/>
+  <dimension ref="A1:AW34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6443,10 +6443,8 @@
           <t>Bikash Thapaliya</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9841873614</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9841873614</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6481,10 +6479,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.73875</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.73875</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -6540,25 +6536,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>L10-1</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.30291</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.30291</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgarde   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
@@ -6644,20 +6636,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M33" s="3" t="inlineStr"/>
       <c r="N33" s="3" t="inlineStr">
         <is>
           <t>Cyrus Shrestha</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9861926855</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9861926855</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -6692,10 +6678,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>27.70284</t>
-        </is>
+      <c r="Y33" s="3" t="n">
+        <v>27.70284</v>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
@@ -6751,50 +6735,257 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.2862</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.28619999999999</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>19h 20m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>19h 20m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
           <t>Case : TV issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>19h 20m</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>19h 20m</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV33" s="3" t="inlineStr">
-        <is>
-          <t>Case : TV issue  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 1:13 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377993</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Yubraj Bhattarai</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Yubraj Bhattarai</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9851110377</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:13:33 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9851110377</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:14:38 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:13:33 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.73578</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>near Fishery Development Directorate  Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>ewarajbhattarai@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>09:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Mamata Bhujel</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>1,10</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.30316</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>4d 58m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -6809,7 +7000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6846,7 +7037,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -6856,7 +7047,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -6867,7 +7058,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>69.7%</t>
         </is>
       </c>
     </row>
@@ -6879,7 +7070,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h 3m</t>
+          <t>7h 42m</t>
         </is>
       </c>
     </row>
@@ -6891,7 +7082,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 58m</t>
+          <t>2d 2h 5m</t>
         </is>
       </c>
     </row>
@@ -6950,14 +7141,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -7104,14 +7295,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8884,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgarde   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -8760,14 +8951,14 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
           <t>Case : TV issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>Case : TV issue  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
           <t>28 Oct 2026 05:39:01 PM</t>
@@ -8791,6 +8982,73 @@
       <c r="M51" s="5" t="inlineStr">
         <is>
           <t>19h 20m</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377993</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Yubraj Bhattarai</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:13:33 PM</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 12:14:38 PM</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:13:33 PM</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>4d 58m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW34"/>
+  <dimension ref="A1:AW38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6845,10 +6845,8 @@
           <t>Yubraj Bhattarai</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9851110377</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9851110377</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -6883,10 +6881,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.73578</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.73578</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -6942,48 +6938,884 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>1,10</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.30316</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.30316000000001</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>4d 58m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS34" s="3" t="inlineStr">
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 1:30 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379448</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Roman Shrestha</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Roman Shrestha</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9828559226</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:30:27 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9828559226</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:54:07 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:30:27 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>27.67445</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Back town of Jyapu Samaj BhawanLonla Tole Marga,Balkumari,Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr"/>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>02:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>CDB635</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>85.33265</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>4d 58m</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 36m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV34" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW34" s="3" t="inlineStr">
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 1:20 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv stb box faulty    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>iptv stb box faulty</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381457</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Kumar</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Kumar</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9812886249</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 03:55:40 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9880141359</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 03:52:15 PM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:20:50 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.687738</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Near KitabKalam Stationery MartKathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>harsh07042@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI36" s="3" t="inlineStr"/>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>4,12</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.297712</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv stb box faulty    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>21h 25m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv stb box faulty    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 1:27 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380053</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Rijal</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Rijal</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9866316594</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:04:29 AM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9866316594</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:04:29 AM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:27:19 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.695898</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Parikar Banquet 44600, Nepal, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>keshabrijal7987@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>22:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>CDB218</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.275775</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 22m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 22m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 1:26 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380053</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Rijal</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Rijal</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9866316594</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:04:29 AM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9866316594</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:04:29 AM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:27:19 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>27.695898</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>Parikar Banquet 44600, Nepal, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>keshabrijal7987@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>22:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>CDB218</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>85.275775</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 22m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 22m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -7000,7 +7832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7037,7 +7869,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -7047,7 +7879,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -7058,7 +7890,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>70.3%</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7902,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 42m</t>
+          <t>10h 41m</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7914,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 5m</t>
+          <t>2d 2h 49m</t>
         </is>
       </c>
     </row>
@@ -7141,14 +7973,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>89.5%</t>
         </is>
       </c>
     </row>
@@ -7159,14 +7991,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -7295,14 +8127,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -7364,14 +8196,14 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -9018,14 +9850,14 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router upgrade   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
           <t>29 Oct 2026 01:13:33 PM</t>
@@ -9049,6 +9881,207 @@
       <c r="M52" s="3" t="inlineStr">
         <is>
           <t>4d 58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>TKT1379448</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Roman Shrestha</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:30:27 PM</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:54:07 PM</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:30:27 PM</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>2d 20h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380053</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Rijal</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:04:29 AM</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:04:29 AM</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:27:19 PM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 22m</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>TKT1380053</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Keshab Rijal</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:04:29 AM</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:04:29 AM</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:27:19 PM</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>2d 2h 22m</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>2d 2h 22m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -7048,10 +7048,8 @@
           <t>Roman Shrestha</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9828559226</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9828559226</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -7086,10 +7084,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>27.67445</t>
-        </is>
+      <c r="Y35" s="3" t="n">
+        <v>27.67445</v>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
@@ -7141,25 +7137,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>CDB635</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>85.33265</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>85.33265</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -7255,10 +7247,8 @@
           <t>Suresh Kumar</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9812886249</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9812886249</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7293,10 +7283,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.687738</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.687738</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -7334,10 +7322,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH36" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH36" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI36" s="3" t="inlineStr"/>
       <c r="AJ36" s="3" t="inlineStr"/>
@@ -7352,25 +7338,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>4,12</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.297712</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.297712</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv stb box faulty    has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -7466,10 +7448,8 @@
           <t>Keshab Rijal</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9866316594</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9866316594</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7504,10 +7484,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.695898</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.695898</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -7563,25 +7541,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>CDB218</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.275775</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.275775</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -7677,10 +7651,8 @@
           <t>Keshab Rijal</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9866316594</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9866316594</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -7715,10 +7687,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>27.695898</t>
-        </is>
+      <c r="Y38" s="3" t="n">
+        <v>27.695898</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -7774,25 +7744,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>CDB218</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>85.275775</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>85.275775</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
@@ -7841,7 +7807,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9917,7 +9883,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -9984,7 +9950,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -10051,7 +10017,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW38"/>
+  <dimension ref="A1:AW39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -7787,6 +7787,209 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 1:49 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379326</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Kushal Gurung</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Kushal Gurung</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9846316207</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:49:49 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>KLK9846316207</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:42:50 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:49:49 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Townplanning samakhushi - Family restaurant P8J8+4C8 Samakhusi Marg 26 Kathmandu 44600, Bagmati, Nep</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>9846316207@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>04:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>3,14</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 6m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7798,7 +8001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7807,7 +8010,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7835,7 +8038,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -7845,7 +8048,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -7856,7 +8059,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>71.1%</t>
         </is>
       </c>
     </row>
@@ -7868,7 +8071,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10h 41m</t>
+          <t>10h 18m</t>
         </is>
       </c>
     </row>
@@ -7880,7 +8083,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 49m</t>
+          <t>2d 3h 32m</t>
         </is>
       </c>
     </row>
@@ -7939,14 +8142,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -8093,14 +8296,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>89.5%</t>
         </is>
       </c>
     </row>
@@ -10051,6 +10254,73 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379326</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Kushal Gurung</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:49:49 PM</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:42:50 PM</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:49:49 PM</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 6m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW39"/>
+  <dimension ref="A1:AW40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7854,10 +7854,8 @@
           <t>Kushal Gurung</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9846316207</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9846316207</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -7947,10 +7945,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
@@ -7961,32 +7957,243 @@
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 6m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS39" s="3" t="inlineStr">
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 2:03 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379893</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Devi Raman Adhikari</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Devi Raman Adhikari</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9801202412</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:03:28 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9801202412</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 09:03:20 AM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:03:28 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Near Srijanshil Boarding School, Madan Bhandari Path, Basanta Marg, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>deviradhikaricmc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>00:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>CDB342</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT39" s="3" t="inlineStr">
-        <is>
-          <t>2d 22h 6m</t>
-        </is>
-      </c>
-      <c r="AU39" s="3" t="inlineStr">
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>2d 5h</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV39" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW39" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -8001,7 +8208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8038,7 +8245,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -8048,7 +8255,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -8059,7 +8266,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>71.8%</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8278,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10h 18m</t>
+          <t>9h 56m</t>
         </is>
       </c>
     </row>
@@ -8083,7 +8290,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 3h 32m</t>
+          <t>2d 3h 35m</t>
         </is>
       </c>
     </row>
@@ -8142,14 +8349,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.5%</t>
         </is>
       </c>
     </row>
@@ -8296,14 +8503,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -10287,14 +10494,14 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
           <t>29 Oct 2026 01:49:49 PM</t>
@@ -10318,6 +10525,73 @@
       <c r="M56" s="3" t="inlineStr">
         <is>
           <t>2d 22h 6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>TKT1379893</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Devi Raman Adhikari</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:03:28 PM</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 09:03:20 AM</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:03:28 PM</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>2d 5h</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW40"/>
+  <dimension ref="A1:AW45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8053,10 +8053,8 @@
           <t>Devi Raman Adhikari</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9801202412</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9801202412</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -8091,10 +8089,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
@@ -8150,50 +8146,1085 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
           <t>CDB342</t>
         </is>
       </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>2d 5h</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS40" s="3" t="inlineStr">
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 2:21 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379348</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Shashi Shrestha</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Shashi Shrestha</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9813316947</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:21:24 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9813316947</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:02:47 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:21:24 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.73944</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Mitho Sagun Sarbottam Pitho Udhyog, Balaju, Kathmandu , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>sasialex21@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>04:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>CDB071</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.30056</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT40" s="3" t="inlineStr">
-        <is>
-          <t>2d 5h</t>
-        </is>
-      </c>
-      <c r="AU40" s="3" t="inlineStr">
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 18m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV40" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW40" s="3" t="inlineStr">
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 2:20 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>no light issue</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379334</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Debraj Sapkota</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Debraj Sapkota</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9841524284</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:20:49 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9841524284</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:48:09 PM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:20:49 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.72891</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Behind SEB School, Susangam Street, Samakhusi - Behind SEB School, Susangam Street", Bagmati, Centra</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>debrajsapkota10@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr"/>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>L25-1</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.31345</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 32m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 2:20 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380419</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Sachyut Vaidya</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Sachyut Vaidya</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9866277798</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:20:50 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9841406619</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 03:24:40 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:20:50 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>27.68521</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Next to Prabhu Bank ATM,Balkhu,Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr"/>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>18:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>85.2973</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 56m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 2:19 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380060</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Thapa</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Thapa</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9843840100</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:19:49 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9843840100</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:11:48 AM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:19:49 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Bible Society - Religious organization M892+243 Bagdol Rd Lalitpur , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>kaalvairab666@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>23:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>3,15</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr"/>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 8m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 2:18 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379585</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Birendra Kumar Chaudhary</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Birendra Kumar Chaudhary</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9841142956</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:18:56 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9841142956</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 06:34:14 PM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:18:56 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.673707</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>M7CW+W6C, Malpokhari Marg, Lalitpur 44700 near Malpokhari Field, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>birendratharu1456@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>01:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.300708</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 44m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -8208,7 +9239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8245,7 +9276,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -8255,7 +9286,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -8266,7 +9297,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -8278,7 +9309,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 56m</t>
+          <t>8h 41m</t>
         </is>
       </c>
     </row>
@@ -8290,7 +9321,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 3h 35m</t>
+          <t>2d 4h 31m</t>
         </is>
       </c>
     </row>
@@ -8349,14 +9380,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>91.7%</t>
         </is>
       </c>
     </row>
@@ -8367,14 +9398,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -8503,14 +9534,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>91.3%</t>
         </is>
       </c>
     </row>
@@ -8549,10 +9580,10 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -8572,14 +9603,14 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -10561,14 +11592,14 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
           <t>29 Oct 2026 02:03:28 PM</t>
@@ -10592,6 +11623,274 @@
       <c r="M57" s="5" t="inlineStr">
         <is>
           <t>2d 5h</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379348</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Shashi Shrestha</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:21:24 PM</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:02:47 PM</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:21:24 PM</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TKT1380419</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Sachyut Vaidya</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:20:50 PM</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 03:24:40 PM</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:20:50 PM</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>1d 22h 56m</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380060</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Thapa</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:19:49 PM</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:11:48 AM</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:19:49 PM</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 8m</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>TKT1379585</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Birendra Kumar Chaudhary</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:18:56 PM</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 06:34:14 PM</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:18:56 PM</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>2d 19h 44m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW45"/>
+  <dimension ref="A1:AW46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8246,20 +8246,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M41" s="3" t="inlineStr"/>
       <c r="N41" s="3" t="inlineStr">
         <is>
           <t>Shashi Shrestha</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9813316947</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9813316947</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8294,10 +8288,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.73944</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.73944</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -8353,25 +8345,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>CDB071</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.30056</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.30056</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -8467,10 +8455,8 @@
           <t>Debraj Sapkota</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9841524284</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9841524284</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -8505,10 +8491,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>27.72891</t>
-        </is>
+      <c r="Y42" s="3" t="n">
+        <v>27.72891</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
@@ -8560,25 +8544,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>L25-1</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.31345</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.31345</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : no light issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -8674,10 +8654,8 @@
           <t>Sachyut Vaidya</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9866277798</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9866277798</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -8712,10 +8690,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>27.68521</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>27.68521</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -8767,25 +8743,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>3,5</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>85.2973</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>85.29730000000001</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
@@ -8881,10 +8853,8 @@
           <t>Ganesh Thapa</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9843840100</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9843840100</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -8974,10 +8944,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
@@ -8988,7 +8956,7 @@
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -9084,10 +9052,8 @@
           <t>Birendra Kumar Chaudhary</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9841142956</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9841142956</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -9122,10 +9088,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.673707</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.673707</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -9181,48 +9145,255 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>1,11</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.300708</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.300708</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 44m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS45" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT45" s="3" t="inlineStr">
-        <is>
-          <t>2d 19h 44m</t>
-        </is>
-      </c>
-      <c r="AU45" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV45" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 2:42 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Setup box connection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Setup box connection</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379446</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Dipesh Nakarmi</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Dipesh Nakarmi</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9863227220</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 06:10:21 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>KLK9863227220</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:53:20 PM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:42:22 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>27.668180453495612, 85.26695337705654, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>dipeshnakarmi3@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>03:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>A03-CDB5</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Setup box connection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 32m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 49m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Setup box connection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
         </is>
@@ -9239,7 +9410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9276,7 +9447,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -9286,7 +9457,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -9297,7 +9468,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -9309,7 +9480,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h 41m</t>
+          <t>9h 46m</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9492,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 4h 31m</t>
+          <t>2d 5h 3m</t>
         </is>
       </c>
     </row>
@@ -9416,14 +9587,14 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -9626,14 +9797,14 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11830,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -11726,7 +11897,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
@@ -11793,7 +11964,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
@@ -11860,14 +12031,14 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
           <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
           <t>29 Oct 2026 02:18:56 PM</t>
@@ -11891,6 +12062,73 @@
       <c r="M61" s="5" t="inlineStr">
         <is>
           <t>2d 19h 44m</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379446</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Dipesh Nakarmi</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Case : Setup box connection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : Setup box connection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 06:10:21 PM</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:53:20 PM</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:42:22 PM</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 32m</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 49m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -9255,10 +9255,8 @@
           <t>Dipesh Nakarmi</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9863227220</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9863227220</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -9293,10 +9291,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -9352,25 +9348,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>A03-CDB5</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>Case : Setup box connection  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
@@ -9419,7 +9411,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -12098,7 +12090,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Case : Setup box connection  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW46"/>
+  <dimension ref="A1:AW48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9391,6 +9391,212 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 3:00 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr"/>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr"/>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr"/>
+      <c r="V47" s="3" t="inlineStr"/>
+      <c r="W47" s="3" t="inlineStr"/>
+      <c r="X47" s="3" t="inlineStr"/>
+      <c r="Y47" s="3" t="inlineStr"/>
+      <c r="Z47" s="3" t="inlineStr"/>
+      <c r="AA47" s="3" t="inlineStr"/>
+      <c r="AB47" s="3" t="inlineStr"/>
+      <c r="AC47" s="3" t="inlineStr"/>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr"/>
+      <c r="AF47" s="3" t="inlineStr"/>
+      <c r="AG47" s="3" t="inlineStr"/>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr"/>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr"/>
+      <c r="AM47" s="3" t="inlineStr"/>
+      <c r="AN47" s="3" t="inlineStr"/>
+      <c r="AO47" s="3" t="inlineStr"/>
+      <c r="AP47" s="3" t="inlineStr"/>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 3:16 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="3" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr"/>
+      <c r="M48" s="3" t="inlineStr"/>
+      <c r="N48" s="3" t="inlineStr"/>
+      <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr"/>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr"/>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr"/>
+      <c r="V48" s="3" t="inlineStr"/>
+      <c r="W48" s="3" t="inlineStr"/>
+      <c r="X48" s="3" t="inlineStr"/>
+      <c r="Y48" s="3" t="inlineStr"/>
+      <c r="Z48" s="3" t="inlineStr"/>
+      <c r="AA48" s="3" t="inlineStr"/>
+      <c r="AB48" s="3" t="inlineStr"/>
+      <c r="AC48" s="3" t="inlineStr"/>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr"/>
+      <c r="AF48" s="3" t="inlineStr"/>
+      <c r="AG48" s="3" t="inlineStr"/>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr"/>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr"/>
+      <c r="AM48" s="3" t="inlineStr"/>
+      <c r="AN48" s="3" t="inlineStr"/>
+      <c r="AO48" s="3" t="inlineStr"/>
+      <c r="AP48" s="3" t="inlineStr"/>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9439,7 +9645,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -9460,7 +9666,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>70.2%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW48"/>
+  <dimension ref="A1:AW49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -9597,6 +9597,213 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 3:45 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb collection  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>stb collection</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376366</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Dil Bahadur Shrestha</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Dil Bahadur Shrestha</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9841497101</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 02:47:02 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9841497101</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 08:58:40 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 03:45:27 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.64958</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-CG Group</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Imadol, Mahalaxmi-4, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>dilbdr123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr"/>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>L49-7</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.34428</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb collection  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>2d 58m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>6d 18h 46m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb collection  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9645,7 +9852,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -9666,7 +9873,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -9749,14 +9956,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>88.0%</t>
         </is>
       </c>
     </row>
@@ -9903,14 +10110,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>21</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW49"/>
+  <dimension ref="A1:AW50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9654,20 +9654,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M49" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M49" s="3" t="inlineStr"/>
       <c r="N49" s="3" t="inlineStr">
         <is>
           <t>Dil Bahadur Shrestha</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9841497101</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9841497101</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -9702,10 +9696,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>27.64958</t>
-        </is>
+      <c r="Y49" s="3" t="n">
+        <v>27.64958</v>
       </c>
       <c r="Z49" s="3" t="inlineStr">
         <is>
@@ -9757,48 +9749,247 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>L49-7</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.34428</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.34428</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>2d 58m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>6d 18h 46m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
           <t>Case : stb collection  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS49" s="3" t="inlineStr">
-        <is>
-          <t>2d 58m</t>
-        </is>
-      </c>
-      <c r="AT49" s="3" t="inlineStr">
-        <is>
-          <t>6d 18h 46m</t>
-        </is>
-      </c>
-      <c r="AU49" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV49" s="3" t="inlineStr">
-        <is>
-          <t>Case : stb collection  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 3:56 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378084</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Raunak Maskay</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Raunak Maskay</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9841126820</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 03:56:01 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841126820</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:05:16 PM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 03:56:01 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr"/>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Bajaj Lainchaur (Star Auto Enterprises) Nagpokhari Marg, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>raunakmaskay@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>11:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>CDB011</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr"/>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>4d 1h 50m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -9815,7 +10006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9824,7 +10015,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9852,7 +10043,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -9862,7 +10053,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -9873,7 +10064,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>69.4%</t>
         </is>
       </c>
     </row>
@@ -9885,7 +10076,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 46m</t>
+          <t>9h 29m</t>
         </is>
       </c>
     </row>
@@ -9897,7 +10088,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 5h 3m</t>
+          <t>2d 6h 22m</t>
         </is>
       </c>
     </row>
@@ -9956,14 +10147,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>88.5%</t>
         </is>
       </c>
     </row>
@@ -10110,14 +10301,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.0%</t>
         </is>
       </c>
     </row>
@@ -12537,6 +12728,73 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>TKT1378084</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Raunak Maskay</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 03:56:01 PM</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:05:16 PM</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 03:56:01 PM</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>4d 1h 50m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW50"/>
+  <dimension ref="A1:AW52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9859,10 +9859,8 @@
           <t>Raunak Maskay</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9841126820</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9841126820</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -9952,10 +9950,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
@@ -9966,30 +9962,444 @@
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>4d 1h 50m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS50" s="3" t="inlineStr">
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 4:12 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380392</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Patwari</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Patwari</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9840091310</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:12:15 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>LTP9840091310</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 03:06:35 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:12:15 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr"/>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>imadol Kamalpokhari, Nepal Bank Limited - Lalitpur Metropolitan, Lalitpur, Bagmati, Nepal, Nepal, Ka</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>9840091310@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>21:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>L43-1</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr"/>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT50" s="3" t="inlineStr">
-        <is>
-          <t>4d 1h 50m</t>
-        </is>
-      </c>
-      <c r="AU50" s="3" t="inlineStr">
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 5m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV50" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW50" s="3" t="inlineStr">
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 4:14 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgarde   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Router upgarde</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381282</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Suresh M Joshi</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Suresh M Joshi</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9851032477</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:14:45 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>sureshjoshi</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 01:23:28 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:14:45 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>27.6731</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Mangal Bazar trilingshwor mahadev, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>evyak.joshi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>12:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>85.32237</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgarde   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 51m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgarde   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -10006,7 +10416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10043,7 +10453,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -10053,7 +10463,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -10064,7 +10474,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>70.6%</t>
         </is>
       </c>
     </row>
@@ -10076,7 +10486,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 29m</t>
+          <t>8h 57m</t>
         </is>
       </c>
     </row>
@@ -10088,7 +10498,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 6h 22m</t>
+          <t>2d 5h 27m</t>
         </is>
       </c>
     </row>
@@ -10147,14 +10557,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>89.3%</t>
         </is>
       </c>
     </row>
@@ -10301,14 +10711,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -12761,14 +13171,14 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
           <t>29 Oct 2026 03:56:01 PM</t>
@@ -12792,6 +13202,140 @@
       <c r="M63" s="5" t="inlineStr">
         <is>
           <t>4d 1h 50m</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380392</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Patwari</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:12:15 PM</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 03:06:35 PM</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:12:15 PM</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>TKT1381282</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Suresh M Joshi</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgarde   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgarde   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:14:45 PM</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 01:23:28 PM</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:14:45 PM</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 51m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -10048,20 +10048,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M51" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M51" s="3" t="inlineStr"/>
       <c r="N51" s="3" t="inlineStr">
         <is>
           <t>Laxman Patwari</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9840091310</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9840091310</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10151,10 +10145,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
@@ -10165,7 +10157,7 @@
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
@@ -10261,10 +10253,8 @@
           <t>Suresh M Joshi</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9851032477</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9851032477</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -10299,10 +10289,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>27.6731</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>27.6731</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -10358,25 +10346,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>1,12</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>85.32237</t>
-        </is>
+      <c r="AP52" s="3" t="n">
+        <v>85.32237000000001</v>
       </c>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgarde   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
@@ -10425,7 +10409,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -13238,7 +13222,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
@@ -13305,7 +13289,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Case : Router upgarde   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW52"/>
+  <dimension ref="A1:AW56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -10389,6 +10389,834 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 4:36 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382320</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Rajan Sharma</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Rajan Sharma</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9819008606</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:36:03 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>9819008606</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:03:31 AM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:36:03 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr"/>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>Near Mantar P94C+MCP, Gothatar Marg, Kageshwori Manohara , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>sharmarajan973@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>06:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>L29-7</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr"/>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>6h 32m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 4:44 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380317</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Brison Maharjan</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Brison Maharjan</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9864156296</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:44:59 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>9864156296</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 02:01:52 PM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:44:59 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr"/>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur ward no 12, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr">
+        <is>
+          <t>Brisonmhrz43@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr">
+        <is>
+          <t>22:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr"/>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 43m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 4:35 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Wifi - 6 Router instal</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379171</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Sharmila Devi Shakya</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Sharmila Devi Shakya</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9841647780</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:30:45 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9841647780</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:30:24 PM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:34:59 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr">
+        <is>
+          <t>27.68652</t>
+        </is>
+      </c>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Near NIC asia Bank, Satungal Chowk, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>ayodhyastha123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>09:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>CDB205A</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>85.25113</t>
+        </is>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>3d 3h 4m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>3d 3h 4m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 4:34 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>Wifi - 6 Router instal</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379171</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Sharmila Devi Shakya</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Sharmila Devi Shakya</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9841647780</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:30:45 PM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>9841647780</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:30:24 PM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:34:59 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr">
+        <is>
+          <t>27.68652</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr"/>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>Near NIC asia Bank, Satungal Chowk, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr">
+        <is>
+          <t>ayodhyastha123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr"/>
+      <c r="AI56" s="3" t="inlineStr">
+        <is>
+          <t>09:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>CDB205A</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>85.25113</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>3d 3h 4m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>3d 3h 4m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10400,7 +11228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10409,7 +11237,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -10437,7 +11265,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -10447,7 +11275,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -10458,7 +11286,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -10470,7 +11298,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h 57m</t>
+          <t>11h 49m</t>
         </is>
       </c>
     </row>
@@ -10482,7 +11310,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 5h 27m</t>
+          <t>2d 5h 17m</t>
         </is>
       </c>
     </row>
@@ -10541,14 +11369,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>90.6%</t>
         </is>
       </c>
     </row>
@@ -10695,14 +11523,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.3%</t>
         </is>
       </c>
     </row>
@@ -13323,6 +14151,274 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382320</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Rajan Sharma</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:36:03 PM</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 10:03:31 AM</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:36:03 PM</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>6h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>TKT1380317</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Brison Maharjan</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:44:59 PM</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 02:01:52 PM</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:44:59 PM</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>2d 2h 43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379171</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Sharmila Devi Shakya</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:30:45 PM</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:30:24 PM</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:34:59 PM</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>3d 3h 4m</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>3d 3h 4m</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>TKT1379171</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Sharmila Devi Shakya</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:30:45 PM</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:30:24 PM</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:34:59 PM</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>3d 3h 4m</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>3d 3h 4m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW56"/>
+  <dimension ref="A1:AW58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10456,10 +10456,8 @@
           <t>Rajan Sharma</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9819008606</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9819008606</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -10549,10 +10547,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
@@ -10563,7 +10559,7 @@
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
@@ -10649,20 +10645,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M54" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M54" s="3" t="inlineStr"/>
       <c r="N54" s="3" t="inlineStr">
         <is>
           <t>Brison Maharjan</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9864156296</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9864156296</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -10752,10 +10742,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
@@ -10766,7 +10754,7 @@
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
@@ -10862,10 +10850,8 @@
           <t>Sharmila Devi Shakya</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9841647780</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9841647780</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -10900,10 +10886,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y55" s="3" t="inlineStr">
-        <is>
-          <t>27.68652</t>
-        </is>
+      <c r="Y55" s="3" t="n">
+        <v>27.68652</v>
       </c>
       <c r="Z55" s="3" t="inlineStr">
         <is>
@@ -10959,25 +10943,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
           <t>CDB205A</t>
         </is>
       </c>
-      <c r="AP55" s="3" t="inlineStr">
-        <is>
-          <t>85.25113</t>
-        </is>
+      <c r="AP55" s="3" t="n">
+        <v>85.25113</v>
       </c>
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
@@ -11073,10 +11053,8 @@
           <t>Sharmila Devi Shakya</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9841647780</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9841647780</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -11111,10 +11089,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y56" s="3" t="inlineStr">
-        <is>
-          <t>27.68652</t>
-        </is>
+      <c r="Y56" s="3" t="n">
+        <v>27.68652</v>
       </c>
       <c r="Z56" s="3" t="inlineStr">
         <is>
@@ -11170,50 +11146,364 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
           <t>CDB205A</t>
         </is>
       </c>
-      <c r="AP56" s="3" t="inlineStr">
-        <is>
-          <t>85.25113</t>
-        </is>
+      <c r="AP56" s="3" t="n">
+        <v>85.25113</v>
       </c>
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>3d 3h 4m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>3d 3h 4m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS56" s="3" t="inlineStr">
-        <is>
-          <t>3d 3h 4m</t>
-        </is>
-      </c>
-      <c r="AT56" s="3" t="inlineStr">
-        <is>
-          <t>3d 3h 4m</t>
-        </is>
-      </c>
-      <c r="AU56" s="3" t="inlineStr">
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 4:54 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr"/>
+      <c r="J57" s="3" t="inlineStr"/>
+      <c r="K57" s="3" t="inlineStr"/>
+      <c r="L57" s="3" t="inlineStr"/>
+      <c r="M57" s="3" t="inlineStr"/>
+      <c r="N57" s="3" t="inlineStr"/>
+      <c r="O57" s="3" t="inlineStr"/>
+      <c r="P57" s="3" t="inlineStr"/>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr"/>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr"/>
+      <c r="V57" s="3" t="inlineStr"/>
+      <c r="W57" s="3" t="inlineStr"/>
+      <c r="X57" s="3" t="inlineStr"/>
+      <c r="Y57" s="3" t="inlineStr"/>
+      <c r="Z57" s="3" t="inlineStr"/>
+      <c r="AA57" s="3" t="inlineStr"/>
+      <c r="AB57" s="3" t="inlineStr"/>
+      <c r="AC57" s="3" t="inlineStr"/>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr"/>
+      <c r="AF57" s="3" t="inlineStr"/>
+      <c r="AG57" s="3" t="inlineStr"/>
+      <c r="AH57" s="3" t="inlineStr"/>
+      <c r="AI57" s="3" t="inlineStr"/>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr"/>
+      <c r="AM57" s="3" t="inlineStr"/>
+      <c r="AN57" s="3" t="inlineStr"/>
+      <c r="AO57" s="3" t="inlineStr"/>
+      <c r="AP57" s="3" t="inlineStr"/>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 4:54 PM</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379366</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Paras Mani Ghimire</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Paras Mani Ghimire</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>9856060074</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:23:16 PM</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>9856060074</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:14:58 PM</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:54:44 PM</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="inlineStr">
+        <is>
+          <t>27.68426</t>
+        </is>
+      </c>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA58" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC58" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD58" s="3" t="inlineStr"/>
+      <c r="AE58" s="3" t="inlineStr">
+        <is>
+          <t>Matatirtha ward no 6 near Shree Jana Kalyan Secondary School, chandragiri, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF58" s="3" t="inlineStr">
+        <is>
+          <t>parashghimire66@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG58" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH58" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI58" s="3" t="inlineStr">
+        <is>
+          <t>06:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ58" s="3" t="inlineStr"/>
+      <c r="AK58" s="3" t="inlineStr"/>
+      <c r="AL58" s="3" t="inlineStr">
+        <is>
+          <t>Bashu Bhat</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>CDB346</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr">
+        <is>
+          <t>85.23489</t>
+        </is>
+      </c>
+      <c r="AQ58" s="3" t="inlineStr"/>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>3d 31m</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>3d 39m</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV56" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW56" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -11265,7 +11555,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -11275,7 +11565,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -11286,7 +11576,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>71.9%</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11588,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>11h 49m</t>
+          <t>13h 18m</t>
         </is>
       </c>
     </row>
@@ -11310,7 +11600,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 5h 17m</t>
+          <t>2d 5h 46m</t>
         </is>
       </c>
     </row>
@@ -11387,14 +11677,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -11592,14 +11882,14 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -14184,7 +14474,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -14251,7 +14541,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -14318,7 +14608,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -14385,14 +14675,14 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
           <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wifi - 6 Router instal   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
           <t>26 Oct 2026 01:30:45 PM</t>
@@ -14416,6 +14706,73 @@
       <c r="M69" s="5" t="inlineStr">
         <is>
           <t>3d 3h 4m</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379366</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Paras Mani Ghimire</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:23:16 PM</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:14:58 PM</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:54:44 PM</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>3d 31m</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>3d 39m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11359,10 +11359,8 @@
           <t>Paras Mani Ghimire</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>9856060074</t>
-        </is>
+      <c r="O58" s="3" t="n">
+        <v>9856060074</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
@@ -11397,10 +11395,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y58" s="3" t="inlineStr">
-        <is>
-          <t>27.68426</t>
-        </is>
+      <c r="Y58" s="3" t="n">
+        <v>27.68426</v>
       </c>
       <c r="Z58" s="3" t="inlineStr">
         <is>
@@ -11438,10 +11434,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH58" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH58" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI58" s="3" t="inlineStr">
         <is>
@@ -11460,25 +11454,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN58" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
           <t>CDB346</t>
         </is>
       </c>
-      <c r="AP58" s="3" t="inlineStr">
-        <is>
-          <t>85.23489</t>
-        </is>
+      <c r="AP58" s="3" t="n">
+        <v>85.23488999999999</v>
       </c>
       <c r="AQ58" s="3" t="inlineStr"/>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
@@ -11527,7 +11517,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -14742,7 +14732,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW58"/>
+  <dimension ref="A1:AW59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11497,6 +11497,217 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 5:23 PM</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381454</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Amir Ratna Shakya</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>Amir Ratna Shakya</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>9841211179</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 05:23:38 PM</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>9841211179</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 03:48:26 PM</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 05:23:38 PM</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr">
+        <is>
+          <t>27.66873</t>
+        </is>
+      </c>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr"/>
+      <c r="AE59" s="3" t="inlineStr">
+        <is>
+          <t>Jyatha Marg, Lalitpur Opposite Of  Ganesh Mandir, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF59" s="3" t="inlineStr">
+        <is>
+          <t>ambhirratna@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="inlineStr"/>
+      <c r="AI59" s="3" t="inlineStr">
+        <is>
+          <t>11:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ59" s="3" t="inlineStr"/>
+      <c r="AK59" s="3" t="inlineStr"/>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM59" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>CDBB42</t>
+        </is>
+      </c>
+      <c r="AP59" s="3" t="inlineStr">
+        <is>
+          <t>85.32638</t>
+        </is>
+      </c>
+      <c r="AQ59" s="3" t="inlineStr"/>
+      <c r="AR59" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 35m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11508,7 +11719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -11517,7 +11728,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -11545,7 +11756,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -11555,7 +11766,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
@@ -11566,7 +11777,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>72.4%</t>
         </is>
       </c>
     </row>
@@ -11578,7 +11789,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>13h 18m</t>
+          <t>12h 59m</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11801,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 5h 46m</t>
+          <t>2d 5h 5m</t>
         </is>
       </c>
     </row>
@@ -11649,14 +11860,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -11803,14 +12014,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.6%</t>
         </is>
       </c>
     </row>
@@ -14766,6 +14977,73 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>TKT1381454</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Amir Ratna Shakya</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 05:23:38 PM</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 03:48:26 PM</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 05:23:38 PM</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 35m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_29_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11564,10 +11564,8 @@
           <t>Amir Ratna Shakya</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>9841211179</t>
-        </is>
+      <c r="O59" s="3" t="n">
+        <v>9841211179</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
@@ -11602,10 +11600,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y59" s="3" t="inlineStr">
-        <is>
-          <t>27.66873</t>
-        </is>
+      <c r="Y59" s="3" t="n">
+        <v>27.66873</v>
       </c>
       <c r="Z59" s="3" t="inlineStr">
         <is>
@@ -11661,25 +11657,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN59" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN59" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
           <t>CDBB42</t>
         </is>
       </c>
-      <c r="AP59" s="3" t="inlineStr">
-        <is>
-          <t>85.32638</t>
-        </is>
+      <c r="AP59" s="3" t="n">
+        <v>85.32638</v>
       </c>
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
@@ -11728,7 +11720,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -15010,7 +15002,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
